--- a/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T16:29:24+00:00</t>
+    <t>2026-09-02T07:15:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:15:34+00:00</t>
+    <t>2026-09-02T11:58:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T11:58:19+00:00</t>
+    <t>2026-09-02T12:35:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T12:35:29+00:00</t>
+    <t>2026-09-02T13:24:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T13:24:46+00:00</t>
+    <t>2026-09-02T15:00:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:00:33+00:00</t>
+    <t>2026-09-02T15:34:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:34:02+00:00</t>
+    <t>2026-09-02T17:45:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:45:23+00:00</t>
+    <t>2026-09-02T17:52:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:09+00:00</t>
+    <t>2026-09-02T18:06:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot.rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:06:21+00:00</t>
+    <t>2026-09-02T20:13:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T20:13:51+00:00</t>
+    <t>2026-09-08T09:14:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:14:04+00:00</t>
+    <t>2026-09-08T11:22:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot.rc4</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:22:39+00:00</t>
+    <t>2026-09-08T11:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
